--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89293911</v>
+        <v>137168046</v>
       </c>
       <c r="B2" t="n">
-        <v>98194</v>
+        <v>96961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kroksjön, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>326882</v>
+        <v>326871</v>
       </c>
       <c r="R2" t="n">
-        <v>6436096</v>
+        <v>6435966</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,27 +770,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293911</t>
+          <t>https://artportalen.se/Sighting/137168046</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89294007</v>
+        <v>137168069</v>
       </c>
       <c r="B3" t="n">
-        <v>98194</v>
+        <v>96961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,17 +822,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327100</v>
+        <v>326900</v>
       </c>
       <c r="R3" t="n">
-        <v>6436185</v>
+        <v>6435944</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,27 +877,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89294007</t>
+          <t>https://artportalen.se/Sighting/137168069</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89293985</v>
+        <v>137168201</v>
       </c>
       <c r="B4" t="n">
-        <v>97977</v>
+        <v>96961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,19 +905,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -933,17 +929,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327043</v>
+        <v>327004</v>
       </c>
       <c r="R4" t="n">
-        <v>6436236</v>
+        <v>6436286</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,27 +984,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293985</t>
+          <t>https://artportalen.se/Sighting/137168201</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89293856</v>
+        <v>137167755</v>
       </c>
       <c r="B5" t="n">
-        <v>97983</v>
+        <v>98040</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,17 +1036,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kroksjön, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>327019</v>
+        <v>326914</v>
       </c>
       <c r="R5" t="n">
-        <v>6435977</v>
+        <v>6436085</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1070,19 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
@@ -1095,27 +1091,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293856</t>
+          <t>https://artportalen.se/Sighting/137167755</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89293870</v>
+        <v>137220344</v>
       </c>
       <c r="B6" t="n">
-        <v>97983</v>
+        <v>96690</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,14 +1143,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroksjön, Svartedalen, Boh</t>
+          <t>Klippvägg, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>326924</v>
+        <v>326891</v>
       </c>
       <c r="R6" t="n">
-        <v>6436035</v>
+        <v>6436244</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,12 +1177,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,27 +1208,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293870</t>
+          <t>https://artportalen.se/Sighting/137220344</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89293960</v>
+        <v>137167987</v>
       </c>
       <c r="B7" t="n">
-        <v>97983</v>
+        <v>96601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,17 +1260,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroksjön, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>326811</v>
+        <v>326859</v>
       </c>
       <c r="R7" t="n">
-        <v>6436048</v>
+        <v>6436000</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,12 +1294,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,27 +1315,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293960</t>
+          <t>https://artportalen.se/Sighting/137167987</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89293980</v>
+        <v>137168132</v>
       </c>
       <c r="B8" t="n">
-        <v>97983</v>
+        <v>96601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,17 +1367,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327043</v>
+        <v>326972</v>
       </c>
       <c r="R8" t="n">
-        <v>6436236</v>
+        <v>6436167</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,27 +1422,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293980</t>
+          <t>https://artportalen.se/Sighting/137168132</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89294003</v>
+        <v>137220328</v>
       </c>
       <c r="B9" t="n">
-        <v>97983</v>
+        <v>96601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,14 +1474,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>327100</v>
+        <v>326966</v>
       </c>
       <c r="R9" t="n">
-        <v>6436185</v>
+        <v>6436123</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,12 +1508,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,27 +1539,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89294003</t>
+          <t>https://artportalen.se/Sighting/137220328</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89294030</v>
+        <v>137220317</v>
       </c>
       <c r="B10" t="n">
-        <v>97983</v>
+        <v>85450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,38 +1567,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>3518</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>327140</v>
+        <v>326902</v>
       </c>
       <c r="R10" t="n">
-        <v>6436207</v>
+        <v>6436053</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,12 +1632,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,27 +1663,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89294030</t>
+          <t>https://artportalen.se/Sighting/137220317</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89294000</v>
+        <v>137167225</v>
       </c>
       <c r="B11" t="n">
-        <v>97986</v>
+        <v>58005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,41 +1691,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>327100</v>
+        <v>327081</v>
       </c>
       <c r="R11" t="n">
-        <v>6436185</v>
+        <v>6436110</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1716,12 +1749,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,34 +1768,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89294000</t>
+          <t>https://artportalen.se/Sighting/137167225</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115231791</v>
+        <v>137167926</v>
       </c>
       <c r="B12" t="n">
-        <v>97975</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,38 +1802,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224361</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>327046</v>
+        <v>326851</v>
       </c>
       <c r="R12" t="n">
-        <v>6436220</v>
+        <v>6436013</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1823,12 +1860,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,25 +1879,2000 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137167926</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137168033</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kroksjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>326842</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6435972</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137168033</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137220369</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kroksjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>326879</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6436206</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137220369</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137220398</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kroksjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>326851</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6435971</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på stubbe. Spillkråkan hördes även i skogen.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137220398</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>89293911</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kroksjön, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>326882</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6436096</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89293911</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>89294007</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>327100</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6436185</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89294007</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137168074</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98449</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kroksjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>326959</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6436024</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137168074</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>89293985</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>327043</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6436236</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89293985</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89293856</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kroksjön, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>327019</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6435977</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89293856</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>89293870</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kroksjön, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>326924</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6436035</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89293870</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>89293960</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kroksjön, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>326811</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6436048</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89293960</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>89293980</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>327043</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6436236</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89293980</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>89294003</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>327100</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6436185</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89294003</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>89294030</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>327140</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6436207</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89294030</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137168161</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kroksjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>327004</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6436293</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ca 100 m2</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137168161</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>89294000</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>327100</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6436185</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-11-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89294000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>115231791</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kringelsjöarna, Boh</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>327046</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6436220</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/115231791</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137167880</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98240</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kroksjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>326799</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6436038</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137167880</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137220362</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98240</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kroksjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>326879</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6436206</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137220362</t>
         </is>
       </c>
     </row>
@@ -1872,6 +3889,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168046</v>
       </c>
       <c r="B2" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137168069</v>
       </c>
       <c r="B3" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137168201</v>
       </c>
       <c r="B4" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137167755</v>
       </c>
       <c r="B5" t="n">
-        <v>98040</v>
+        <v>98053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137220344</v>
       </c>
       <c r="B6" t="n">
-        <v>96690</v>
+        <v>96703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137167987</v>
       </c>
       <c r="B7" t="n">
-        <v>96601</v>
+        <v>96614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137168132</v>
       </c>
       <c r="B8" t="n">
-        <v>96601</v>
+        <v>96614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137220328</v>
       </c>
       <c r="B9" t="n">
-        <v>96601</v>
+        <v>96614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>137220317</v>
       </c>
       <c r="B10" t="n">
-        <v>85450</v>
+        <v>85463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137167225</v>
       </c>
       <c r="B11" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137167926</v>
       </c>
       <c r="B12" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>137168033</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137220369</v>
       </c>
       <c r="B14" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137220398</v>
       </c>
       <c r="B15" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>137168074</v>
       </c>
       <c r="B18" t="n">
-        <v>98449</v>
+        <v>98462</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>137168161</v>
       </c>
       <c r="B26" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>137167880</v>
       </c>
       <c r="B29" t="n">
-        <v>98240</v>
+        <v>98253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>137220362</v>
       </c>
       <c r="B30" t="n">
-        <v>98240</v>
+        <v>98253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168046</v>
       </c>
       <c r="B2" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137168069</v>
       </c>
       <c r="B3" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137168201</v>
       </c>
       <c r="B4" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137167755</v>
       </c>
       <c r="B5" t="n">
-        <v>98053</v>
+        <v>98055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137220344</v>
       </c>
       <c r="B6" t="n">
-        <v>96703</v>
+        <v>96705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137167987</v>
       </c>
       <c r="B7" t="n">
-        <v>96614</v>
+        <v>96616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137168132</v>
       </c>
       <c r="B8" t="n">
-        <v>96614</v>
+        <v>96616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137220328</v>
       </c>
       <c r="B9" t="n">
-        <v>96614</v>
+        <v>96616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>137220317</v>
       </c>
       <c r="B10" t="n">
-        <v>85463</v>
+        <v>85465</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137167225</v>
       </c>
       <c r="B11" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137167926</v>
       </c>
       <c r="B12" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>137168033</v>
       </c>
       <c r="B13" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137220369</v>
       </c>
       <c r="B14" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137220398</v>
       </c>
       <c r="B15" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>137168074</v>
       </c>
       <c r="B18" t="n">
-        <v>98462</v>
+        <v>98464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>137168161</v>
       </c>
       <c r="B26" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>137167880</v>
       </c>
       <c r="B29" t="n">
-        <v>98253</v>
+        <v>98255</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>137220362</v>
       </c>
       <c r="B30" t="n">
-        <v>98253</v>
+        <v>98255</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -2160,11 +2160,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168046</v>
       </c>
       <c r="B2" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137168069</v>
       </c>
       <c r="B3" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137168201</v>
       </c>
       <c r="B4" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137167755</v>
       </c>
       <c r="B5" t="n">
-        <v>98055</v>
+        <v>98058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137220344</v>
       </c>
       <c r="B6" t="n">
-        <v>96705</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137167987</v>
       </c>
       <c r="B7" t="n">
-        <v>96616</v>
+        <v>96619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137168132</v>
       </c>
       <c r="B8" t="n">
-        <v>96616</v>
+        <v>96619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137220328</v>
       </c>
       <c r="B9" t="n">
-        <v>96616</v>
+        <v>96619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>137220317</v>
       </c>
       <c r="B10" t="n">
-        <v>85465</v>
+        <v>85468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137168074</v>
       </c>
       <c r="B18" t="n">
-        <v>98464</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137168161</v>
       </c>
       <c r="B26" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>137167880</v>
       </c>
       <c r="B29" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137220362</v>
       </c>
       <c r="B30" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168046</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137168069</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137168201</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137167755</v>
       </c>
       <c r="B5" t="n">
-        <v>98058</v>
+        <v>98068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137220344</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137167987</v>
       </c>
       <c r="B7" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137168132</v>
       </c>
       <c r="B8" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137220328</v>
       </c>
       <c r="B9" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>137220317</v>
       </c>
       <c r="B10" t="n">
-        <v>85468</v>
+        <v>85478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137167225</v>
       </c>
       <c r="B11" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137167926</v>
       </c>
       <c r="B12" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>137168033</v>
       </c>
       <c r="B13" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137220369</v>
       </c>
       <c r="B14" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>137220398</v>
       </c>
       <c r="B15" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137168074</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98477</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137168161</v>
       </c>
       <c r="B26" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>137167880</v>
       </c>
       <c r="B29" t="n">
-        <v>98258</v>
+        <v>98268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137220362</v>
       </c>
       <c r="B30" t="n">
-        <v>98258</v>
+        <v>98268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137168046</v>
       </c>
       <c r="B2" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137168069</v>
       </c>
       <c r="B3" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137168201</v>
       </c>
       <c r="B4" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137167755</v>
       </c>
       <c r="B5" t="n">
-        <v>98068</v>
+        <v>98069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137220344</v>
       </c>
       <c r="B6" t="n">
-        <v>96718</v>
+        <v>96719</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>137167987</v>
       </c>
       <c r="B7" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137168132</v>
       </c>
       <c r="B8" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137220328</v>
       </c>
       <c r="B9" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137168074</v>
       </c>
       <c r="B18" t="n">
-        <v>98477</v>
+        <v>98478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137168161</v>
       </c>
       <c r="B26" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>137167880</v>
       </c>
       <c r="B29" t="n">
-        <v>98268</v>
+        <v>98269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137220362</v>
       </c>
       <c r="B30" t="n">
-        <v>98268</v>
+        <v>98269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,38 +680,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137168046</v>
+        <v>137356152</v>
       </c>
       <c r="B2" t="n">
-        <v>96990</v>
+        <v>93401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>2075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>326871</v>
+        <v>326942</v>
       </c>
       <c r="R2" t="n">
-        <v>6435966</v>
+        <v>6436176</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På ett flertal äldre liggande ek stockar i närheten.  Medobservatör Magnus Vinqvist.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,30 +771,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Patrik  Hammargren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Patrik  Hammargren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137168046</t>
+          <t>https://artportalen.se/Sighting/137356152</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137168069</v>
+        <v>137168046</v>
       </c>
       <c r="B3" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>326900</v>
+        <v>326871</v>
       </c>
       <c r="R3" t="n">
-        <v>6435944</v>
+        <v>6435966</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,16 +902,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137168069</t>
+          <t>https://artportalen.se/Sighting/137168046</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137168201</v>
+        <v>137168069</v>
       </c>
       <c r="B4" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327004</v>
+        <v>326900</v>
       </c>
       <c r="R4" t="n">
-        <v>6436286</v>
+        <v>6435944</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,16 +1009,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137168201</t>
+          <t>https://artportalen.se/Sighting/137168069</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137167755</v>
+        <v>137168201</v>
       </c>
       <c r="B5" t="n">
-        <v>98069</v>
+        <v>96995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>326914</v>
+        <v>327004</v>
       </c>
       <c r="R5" t="n">
-        <v>6436085</v>
+        <v>6436286</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
@@ -1102,16 +1116,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137167755</t>
+          <t>https://artportalen.se/Sighting/137168201</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137220344</v>
+        <v>137167755</v>
       </c>
       <c r="B6" t="n">
-        <v>96719</v>
+        <v>98074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,17 +1157,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klippvägg, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>326891</v>
+        <v>326914</v>
       </c>
       <c r="R6" t="n">
-        <v>6436244</v>
+        <v>6436085</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,29 +1191,19 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
@@ -1208,27 +1212,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220344</t>
+          <t>https://artportalen.se/Sighting/137167755</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137167987</v>
+        <v>137220344</v>
       </c>
       <c r="B7" t="n">
-        <v>96630</v>
+        <v>96724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,17 +1264,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroksjön, Boh</t>
+          <t>Klippvägg, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>326859</v>
+        <v>326891</v>
       </c>
       <c r="R7" t="n">
-        <v>6436000</v>
+        <v>6436244</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,12 +1298,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,27 +1329,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137167987</t>
+          <t>https://artportalen.se/Sighting/137220344</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137168132</v>
+        <v>137167987</v>
       </c>
       <c r="B8" t="n">
-        <v>96630</v>
+        <v>96635</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>326972</v>
+        <v>326859</v>
       </c>
       <c r="R8" t="n">
-        <v>6436167</v>
+        <v>6436000</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,16 +1447,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137168132</t>
+          <t>https://artportalen.se/Sighting/137167987</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137220328</v>
+        <v>137168132</v>
       </c>
       <c r="B9" t="n">
-        <v>96630</v>
+        <v>96635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,13 +1492,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>326966</v>
+        <v>326972</v>
       </c>
       <c r="R9" t="n">
-        <v>6436123</v>
+        <v>6436167</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1508,22 +1522,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,27 +1543,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220328</t>
+          <t>https://artportalen.se/Sighting/137168132</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137220317</v>
+        <v>137220328</v>
       </c>
       <c r="B10" t="n">
-        <v>85478</v>
+        <v>96635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,34 +1571,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3518</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1602,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>326902</v>
+        <v>326966</v>
       </c>
       <c r="R10" t="n">
-        <v>6436053</v>
+        <v>6436123</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,16 +1671,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220317</t>
+          <t>https://artportalen.se/Sighting/137220328</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137167225</v>
+        <v>137220317</v>
       </c>
       <c r="B11" t="n">
-        <v>58030</v>
+        <v>85481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,27 +1688,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>3518</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1719,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>327081</v>
+        <v>326902</v>
       </c>
       <c r="R11" t="n">
-        <v>6436110</v>
+        <v>6436053</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,17 +1753,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,33 +1777,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137167225</t>
+          <t>https://artportalen.se/Sighting/137220317</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137167926</v>
+        <v>137167225</v>
       </c>
       <c r="B12" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>326851</v>
+        <v>327081</v>
       </c>
       <c r="R12" t="n">
-        <v>6436013</v>
+        <v>6436110</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,16 +1906,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137167926</t>
+          <t>https://artportalen.se/Sighting/137167225</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137168033</v>
+        <v>137167926</v>
       </c>
       <c r="B13" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>326842</v>
+        <v>326851</v>
       </c>
       <c r="R13" t="n">
-        <v>6435972</v>
+        <v>6436013</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1981,7 +1991,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,16 +2017,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137168033</t>
+          <t>https://artportalen.se/Sighting/137167926</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137220369</v>
+        <v>137168033</v>
       </c>
       <c r="B14" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,13 +2062,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>326879</v>
+        <v>326842</v>
       </c>
       <c r="R14" t="n">
-        <v>6436206</v>
+        <v>6435972</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,22 +2092,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,27 +2117,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220369</t>
+          <t>https://artportalen.se/Sighting/137168033</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137220398</v>
+        <v>137220369</v>
       </c>
       <c r="B15" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>326851</v>
+        <v>326879</v>
       </c>
       <c r="R15" t="n">
-        <v>6435971</v>
+        <v>6436206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,11 +2221,6 @@
           <t>13:30</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska spår av födosök på stubbe. Spillkråkan hördes även i skogen.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2244,16 +2244,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220398</t>
+          <t>https://artportalen.se/Sighting/137220369</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89293911</v>
+        <v>137220398</v>
       </c>
       <c r="B16" t="n">
-        <v>98194</v>
+        <v>58031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,46 +2261,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220686</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroksjön, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>326882</v>
+        <v>326851</v>
       </c>
       <c r="R16" t="n">
-        <v>6436096</v>
+        <v>6435971</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,12 +2319,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska spår av födosök på stubbe. Spillkråkan hördes även i skogen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,31 +2348,30 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293911</t>
+          <t>https://artportalen.se/Sighting/137220398</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89294007</v>
+        <v>89293911</v>
       </c>
       <c r="B17" t="n">
         <v>98194</v>
@@ -2393,21 +2399,29 @@
           <t>(L.) Roth</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>327100</v>
+        <v>326882</v>
       </c>
       <c r="R17" t="n">
-        <v>6436185</v>
+        <v>6436096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,16 +2480,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89294007</t>
+          <t>https://artportalen.se/Sighting/89293911</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137168074</v>
+        <v>89294007</v>
       </c>
       <c r="B18" t="n">
-        <v>98478</v>
+        <v>98194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,17 +2521,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kroksjön, Boh</t>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>326959</v>
+        <v>327100</v>
       </c>
       <c r="R18" t="n">
-        <v>6436024</v>
+        <v>6436185</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2541,12 +2555,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2020-11-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2020-11-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,27 +2576,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137168074</t>
+          <t>https://artportalen.se/Sighting/89294007</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89293985</v>
+        <v>137168074</v>
       </c>
       <c r="B19" t="n">
-        <v>97977</v>
+        <v>98483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,19 +2604,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221944</v>
+        <v>220686</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -2610,17 +2628,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>327043</v>
+        <v>326959</v>
       </c>
       <c r="R19" t="n">
-        <v>6436236</v>
+        <v>6436024</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,12 +2662,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,27 +2683,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293985</t>
+          <t>https://artportalen.se/Sighting/137168074</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89293856</v>
+        <v>89293985</v>
       </c>
       <c r="B20" t="n">
-        <v>97983</v>
+        <v>97977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,23 +2711,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -2717,14 +2731,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroksjön, Svartedalen, Boh</t>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>327019</v>
+        <v>327043</v>
       </c>
       <c r="R20" t="n">
-        <v>6435977</v>
+        <v>6436236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,13 +2797,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293856</t>
+          <t>https://artportalen.se/Sighting/89293985</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89293870</v>
+        <v>89293856</v>
       </c>
       <c r="B21" t="n">
         <v>97983</v>
@@ -2828,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>326924</v>
+        <v>327019</v>
       </c>
       <c r="R21" t="n">
-        <v>6436035</v>
+        <v>6435977</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,13 +2904,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293870</t>
+          <t>https://artportalen.se/Sighting/89293856</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89293960</v>
+        <v>89293870</v>
       </c>
       <c r="B22" t="n">
         <v>97983</v>
@@ -2935,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>326811</v>
+        <v>326924</v>
       </c>
       <c r="R22" t="n">
-        <v>6436048</v>
+        <v>6436035</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2997,13 +3011,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293960</t>
+          <t>https://artportalen.se/Sighting/89293870</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89293980</v>
+        <v>89293960</v>
       </c>
       <c r="B23" t="n">
         <v>97983</v>
@@ -3038,14 +3052,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>327043</v>
+        <v>326811</v>
       </c>
       <c r="R23" t="n">
-        <v>6436236</v>
+        <v>6436048</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3104,13 +3118,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89293980</t>
+          <t>https://artportalen.se/Sighting/89293960</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89294003</v>
+        <v>89293980</v>
       </c>
       <c r="B24" t="n">
         <v>97983</v>
@@ -3149,10 +3163,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>327100</v>
+        <v>327043</v>
       </c>
       <c r="R24" t="n">
-        <v>6436185</v>
+        <v>6436236</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3211,13 +3225,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89294003</t>
+          <t>https://artportalen.se/Sighting/89293980</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89294030</v>
+        <v>89294003</v>
       </c>
       <c r="B25" t="n">
         <v>97983</v>
@@ -3256,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>327140</v>
+        <v>327100</v>
       </c>
       <c r="R25" t="n">
-        <v>6436207</v>
+        <v>6436185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,16 +3332,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89294030</t>
+          <t>https://artportalen.se/Sighting/89294003</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137168161</v>
+        <v>89294030</v>
       </c>
       <c r="B26" t="n">
-        <v>98267</v>
+        <v>97983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,17 +3373,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kroksjön, Boh</t>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>327004</v>
+        <v>327140</v>
       </c>
       <c r="R26" t="n">
-        <v>6436293</v>
+        <v>6436207</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3393,17 +3407,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2020-11-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ca 100 m2</t>
+          <t>2020-11-28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3419,27 +3428,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137168161</t>
+          <t>https://artportalen.se/Sighting/89294030</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89294000</v>
+        <v>137168161</v>
       </c>
       <c r="B27" t="n">
-        <v>97986</v>
+        <v>98272</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3447,16 +3456,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3471,17 +3480,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Svartedalen, Boh</t>
+          <t>Kroksjön, Boh</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>327100</v>
+        <v>327004</v>
       </c>
       <c r="R27" t="n">
-        <v>6436185</v>
+        <v>6436293</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3505,12 +3514,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-11-28</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 100 m2</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3526,27 +3540,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89294000</t>
+          <t>https://artportalen.se/Sighting/137168161</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115231791</v>
+        <v>89294000</v>
       </c>
       <c r="B28" t="n">
-        <v>97975</v>
+        <v>97986</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,21 +3568,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>224361</v>
+        <v>221946</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3578,17 +3592,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kringelsjöarna, Boh</t>
+          <t>Kringelsjöarna, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>327046</v>
+        <v>327100</v>
       </c>
       <c r="R28" t="n">
-        <v>6436220</v>
+        <v>6436185</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3612,12 +3626,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2020-11-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2020-11-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3644,16 +3658,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115231791</t>
+          <t>https://artportalen.se/Sighting/89294000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137167880</v>
+        <v>115231791</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
+        <v>97975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,19 +3675,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>224363</v>
+        <v>224361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -3681,14 +3699,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kroksjön, Boh</t>
+          <t>Kringelsjöarna, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>326799</v>
+        <v>327046</v>
       </c>
       <c r="R29" t="n">
-        <v>6436038</v>
+        <v>6436220</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3715,12 +3733,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3736,27 +3754,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137167880</t>
+          <t>https://artportalen.se/Sighting/115231791</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137220362</v>
+        <v>137167880</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
+        <v>98274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3777,16 +3795,8 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3796,13 +3806,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>326879</v>
+        <v>326799</v>
       </c>
       <c r="R30" t="n">
-        <v>6436206</v>
+        <v>6436038</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3826,22 +3836,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3857,16 +3857,137 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137167880</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137220362</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98274</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kroksjön, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>326879</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6436206</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Västerlanda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137220362</t>
         </is>
@@ -3903,6 +4024,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137356152</v>
       </c>
       <c r="B2" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137168046</v>
       </c>
       <c r="B3" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137168069</v>
       </c>
       <c r="B4" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137168201</v>
       </c>
       <c r="B5" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137167755</v>
       </c>
       <c r="B6" t="n">
-        <v>98074</v>
+        <v>98076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137220344</v>
       </c>
       <c r="B7" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137167987</v>
       </c>
       <c r="B8" t="n">
-        <v>96635</v>
+        <v>96637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>137168132</v>
       </c>
       <c r="B9" t="n">
-        <v>96635</v>
+        <v>96637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>137220328</v>
       </c>
       <c r="B10" t="n">
-        <v>96635</v>
+        <v>96637</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>137168074</v>
       </c>
       <c r="B19" t="n">
-        <v>98483</v>
+        <v>98485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137168161</v>
       </c>
       <c r="B27" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>137167880</v>
       </c>
       <c r="B30" t="n">
-        <v>98274</v>
+        <v>98276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>137220362</v>
       </c>
       <c r="B31" t="n">
-        <v>98274</v>
+        <v>98276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137356152</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137168046</v>
       </c>
       <c r="B3" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137168069</v>
       </c>
       <c r="B4" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137168201</v>
       </c>
       <c r="B5" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137167755</v>
       </c>
       <c r="B6" t="n">
-        <v>98076</v>
+        <v>98082</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137220344</v>
       </c>
       <c r="B7" t="n">
-        <v>96726</v>
+        <v>96732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137167987</v>
       </c>
       <c r="B8" t="n">
-        <v>96637</v>
+        <v>96643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>137168132</v>
       </c>
       <c r="B9" t="n">
-        <v>96637</v>
+        <v>96643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>137220328</v>
       </c>
       <c r="B10" t="n">
-        <v>96637</v>
+        <v>96643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>137220317</v>
       </c>
       <c r="B11" t="n">
-        <v>85481</v>
+        <v>85486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137167225</v>
       </c>
       <c r="B12" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137167926</v>
       </c>
       <c r="B13" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>137168033</v>
       </c>
       <c r="B14" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137220369</v>
       </c>
       <c r="B15" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137220398</v>
       </c>
       <c r="B16" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>137168074</v>
       </c>
       <c r="B19" t="n">
-        <v>98485</v>
+        <v>98491</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137168161</v>
       </c>
       <c r="B27" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>137167880</v>
       </c>
       <c r="B30" t="n">
-        <v>98276</v>
+        <v>98282</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>137220362</v>
       </c>
       <c r="B31" t="n">
-        <v>98276</v>
+        <v>98282</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137356152</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137168046</v>
       </c>
       <c r="B3" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137168069</v>
       </c>
       <c r="B4" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137168201</v>
       </c>
       <c r="B5" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137167755</v>
       </c>
       <c r="B6" t="n">
-        <v>98082</v>
+        <v>98094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137220344</v>
       </c>
       <c r="B7" t="n">
-        <v>96732</v>
+        <v>96744</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137167987</v>
       </c>
       <c r="B8" t="n">
-        <v>96643</v>
+        <v>96655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>137168132</v>
       </c>
       <c r="B9" t="n">
-        <v>96643</v>
+        <v>96655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>137220328</v>
       </c>
       <c r="B10" t="n">
-        <v>96643</v>
+        <v>96655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>137220317</v>
       </c>
       <c r="B11" t="n">
-        <v>85486</v>
+        <v>85497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>137168074</v>
       </c>
       <c r="B19" t="n">
-        <v>98491</v>
+        <v>98503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137168161</v>
       </c>
       <c r="B27" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>137167880</v>
       </c>
       <c r="B30" t="n">
-        <v>98282</v>
+        <v>98294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>137220362</v>
       </c>
       <c r="B31" t="n">
-        <v>98282</v>
+        <v>98294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137356152</v>
       </c>
       <c r="B2" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137168046</v>
       </c>
       <c r="B3" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137168069</v>
       </c>
       <c r="B4" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137168201</v>
       </c>
       <c r="B5" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137167755</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137220344</v>
       </c>
       <c r="B7" t="n">
-        <v>96744</v>
+        <v>96745</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137167987</v>
       </c>
       <c r="B8" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>137168132</v>
       </c>
       <c r="B9" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>137220328</v>
       </c>
       <c r="B10" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>137220317</v>
       </c>
       <c r="B11" t="n">
-        <v>85497</v>
+        <v>85498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>137168074</v>
       </c>
       <c r="B19" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137168161</v>
       </c>
       <c r="B27" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>137167880</v>
       </c>
       <c r="B30" t="n">
-        <v>98294</v>
+        <v>98295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>137220362</v>
       </c>
       <c r="B31" t="n">
-        <v>98294</v>
+        <v>98295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137356152</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137168046</v>
       </c>
       <c r="B3" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137168069</v>
       </c>
       <c r="B4" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137168201</v>
       </c>
       <c r="B5" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137167755</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137220344</v>
       </c>
       <c r="B7" t="n">
-        <v>96745</v>
+        <v>96748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137167987</v>
       </c>
       <c r="B8" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>137168132</v>
       </c>
       <c r="B9" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>137220328</v>
       </c>
       <c r="B10" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>137220317</v>
       </c>
       <c r="B11" t="n">
-        <v>85498</v>
+        <v>85501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>137168074</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137168161</v>
       </c>
       <c r="B27" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>137167880</v>
       </c>
       <c r="B30" t="n">
-        <v>98295</v>
+        <v>98298</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>137220362</v>
       </c>
       <c r="B31" t="n">
-        <v>98295</v>
+        <v>98298</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 40487-2026 artfynd.xlsx
+++ b/artfynd/A 40487-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137356152</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137168046</v>
       </c>
       <c r="B3" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137168069</v>
       </c>
       <c r="B4" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137168201</v>
       </c>
       <c r="B5" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>137167755</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137220344</v>
       </c>
       <c r="B7" t="n">
-        <v>96748</v>
+        <v>96752</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137167987</v>
       </c>
       <c r="B8" t="n">
-        <v>96659</v>
+        <v>96663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>137168132</v>
       </c>
       <c r="B9" t="n">
-        <v>96659</v>
+        <v>96663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>137220328</v>
       </c>
       <c r="B10" t="n">
-        <v>96659</v>
+        <v>96663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>137220317</v>
       </c>
       <c r="B11" t="n">
-        <v>85501</v>
+        <v>85505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137167225</v>
       </c>
       <c r="B12" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137167926</v>
       </c>
       <c r="B13" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>137168033</v>
       </c>
       <c r="B14" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137220369</v>
       </c>
       <c r="B15" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137220398</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>137168074</v>
       </c>
       <c r="B19" t="n">
-        <v>98507</v>
+        <v>98511</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137168161</v>
       </c>
       <c r="B27" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>137167880</v>
       </c>
       <c r="B30" t="n">
-        <v>98298</v>
+        <v>98302</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>137220362</v>
       </c>
       <c r="B31" t="n">
-        <v>98298</v>
+        <v>98302</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
